--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -681,7 +681,7 @@
     <t>书页</t>
   </si>
   <si>
-    <t>升级技能，获得10点技能经验</t>
+    <t>升级技能，获得5点技能经验</t>
   </si>
   <si>
     <t>灵盾碎片</t>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="314">
   <si>
     <t>_Id</t>
   </si>
@@ -738,6 +738,30 @@
     <t>神兵进阶到5阶的材料</t>
   </si>
   <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>分解红装获取，红装锻造材料</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>分解金装获取，红装锻造材料</t>
+  </si>
+  <si>
+    <t>红色魂晶</t>
+  </si>
+  <si>
+    <t>红色宠物培养材料</t>
+  </si>
+  <si>
+    <t>金色魂晶</t>
+  </si>
+  <si>
+    <t>金色宠物培养材料</t>
+  </si>
+  <si>
     <t>等级丹</t>
   </si>
   <si>
@@ -750,258 +774,6 @@
     <t>天赋经验+500</t>
   </si>
   <si>
-    <t>魂环碎片</t>
-  </si>
-  <si>
-    <t>合成魂环的材料</t>
-  </si>
-  <si>
-    <t>精炼石</t>
-  </si>
-  <si>
-    <t>装备精练材料</t>
-  </si>
-  <si>
-    <t>装备副本卷</t>
-  </si>
-  <si>
-    <t>装备副本次数+1，全部使用最多一次性使用5000张</t>
-  </si>
-  <si>
-    <t>BOSS挑战卷</t>
-  </si>
-  <si>
-    <t>挑战BOSS之家</t>
-  </si>
-  <si>
-    <t>专属碎片</t>
-  </si>
-  <si>
-    <t>兑换专属自选包</t>
-  </si>
-  <si>
-    <t>四格碎片</t>
-  </si>
-  <si>
-    <t>升级四格</t>
-  </si>
-  <si>
-    <t>凤凰之羽</t>
-  </si>
-  <si>
-    <t>合成或者升级翅膀</t>
-  </si>
-  <si>
-    <t>专属精华</t>
-  </si>
-  <si>
-    <t>废弃道具</t>
-  </si>
-  <si>
-    <t>专属之心</t>
-  </si>
-  <si>
-    <t>升级专属</t>
-  </si>
-  <si>
-    <t>红装精华</t>
-  </si>
-  <si>
-    <t>分解红装获取，红装升阶材料，红装随机属性强化材料</t>
-  </si>
-  <si>
-    <t>传世挑战卷</t>
-  </si>
-  <si>
-    <t>传世挑战次数+1</t>
-  </si>
-  <si>
-    <t>红装粉尘</t>
-  </si>
-  <si>
-    <t>分解红装石头获取，合成红装精华</t>
-  </si>
-  <si>
-    <t>练体丹</t>
-  </si>
-  <si>
-    <t>修炼材料</t>
-  </si>
-  <si>
-    <t>幻境挑战卷</t>
-  </si>
-  <si>
-    <t>幻境挑战时间+60S</t>
-  </si>
-  <si>
-    <t>遗物粉尘</t>
-  </si>
-  <si>
-    <t>分解遗物获取，每10个可以替代1个遗物，升级任意已经激活过的遗物</t>
-  </si>
-  <si>
-    <t>金装精华</t>
-  </si>
-  <si>
-    <t>分解金装获取，金装升阶材料</t>
-  </si>
-  <si>
-    <t>改造石</t>
-  </si>
-  <si>
-    <t>装备改造材料</t>
-  </si>
-  <si>
-    <t>口粮</t>
-  </si>
-  <si>
-    <t>魂宠升级材料</t>
-  </si>
-  <si>
-    <t>橙色魂心</t>
-  </si>
-  <si>
-    <t>橙色魂宠进阶材料</t>
-  </si>
-  <si>
-    <t>红色魂心</t>
-  </si>
-  <si>
-    <t>红色魂宠进阶材料</t>
-  </si>
-  <si>
-    <t>金色魂心</t>
-  </si>
-  <si>
-    <t>金色魂宠进阶材料</t>
-  </si>
-  <si>
-    <t>暗金精华</t>
-  </si>
-  <si>
-    <t>分解暗金装备获取，暗金装备升阶材料</t>
-  </si>
-  <si>
-    <t>开孔石</t>
-  </si>
-  <si>
-    <t>给宝石增加镶嵌孔</t>
-  </si>
-  <si>
-    <t>青龙精华</t>
-  </si>
-  <si>
-    <t>兑换青龙神器自选</t>
-  </si>
-  <si>
-    <t>白虎精华</t>
-  </si>
-  <si>
-    <t>兑换白虎神器自选</t>
-  </si>
-  <si>
-    <t>朱雀精华</t>
-  </si>
-  <si>
-    <t>兑换朱雀神器自选</t>
-  </si>
-  <si>
-    <t>玄武精华</t>
-  </si>
-  <si>
-    <t>兑换玄武神器自选</t>
-  </si>
-  <si>
-    <t>麒麟精华</t>
-  </si>
-  <si>
-    <t>兑换麒麟神器自选</t>
-  </si>
-  <si>
-    <t>行气丹</t>
-  </si>
-  <si>
-    <t>时装精华</t>
-  </si>
-  <si>
-    <t>激活上阵时装</t>
-  </si>
-  <si>
-    <t>升阶传奇专属的材料</t>
-  </si>
-  <si>
-    <t>永恒精华</t>
-  </si>
-  <si>
-    <t>升阶永恒专属的材料</t>
-  </si>
-  <si>
-    <t>混沌精华</t>
-  </si>
-  <si>
-    <t>分解粉色混沌装备获取，混沌装备升阶材料</t>
-  </si>
-  <si>
-    <t>不朽精华</t>
-  </si>
-  <si>
-    <t>升阶不朽专属的材料</t>
-  </si>
-  <si>
-    <t>炼神丹</t>
-  </si>
-  <si>
-    <t>暗金魂心</t>
-  </si>
-  <si>
-    <t>神宠进阶材料</t>
-  </si>
-  <si>
-    <t>生肖精华</t>
-  </si>
-  <si>
-    <t>升级生肖的材料</t>
-  </si>
-  <si>
-    <t>生肖本源</t>
-  </si>
-  <si>
-    <t>生肖心核</t>
-  </si>
-  <si>
-    <t>升阶生肖的材料</t>
-  </si>
-  <si>
-    <t>图鉴碎片</t>
-  </si>
-  <si>
-    <t>兑换万能图鉴的碎片</t>
-  </si>
-  <si>
-    <t>龙城勋章</t>
-  </si>
-  <si>
-    <t>周年庆活动材料，兑换其他道具</t>
-  </si>
-  <si>
-    <t>超级书页</t>
-  </si>
-  <si>
-    <t>兑换12阶技能</t>
-  </si>
-  <si>
-    <t>欢乐精粹</t>
-  </si>
-  <si>
-    <t>节日副本掉落</t>
-  </si>
-  <si>
-    <t>橙装精华</t>
-  </si>
-  <si>
-    <t>升级或洗练红装，或者回收为1000精炼石</t>
-  </si>
-  <si>
     <t>十年魂环</t>
   </si>
   <si>
@@ -1236,64 +1008,112 @@
     <t>骨弓</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em13</t>
+  </si>
+  <si>
     <t>迷雾森林珍宝材料</t>
   </si>
   <si>
     <t>骨杖</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em14</t>
+  </si>
+  <si>
     <t>骨龙核心</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em15</t>
+  </si>
+  <si>
     <t>獠牙</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em16</t>
+  </si>
+  <si>
     <t>蛮鬃林地珍宝材料</t>
   </si>
   <si>
     <t>图腾</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em17</t>
+  </si>
+  <si>
     <t>酋长重锤</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em18</t>
+  </si>
+  <si>
     <t>‌血花露‌</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em19</t>
+  </si>
+  <si>
     <t>熔火地穴珍宝材料</t>
   </si>
   <si>
     <t>火甲虫</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em20</t>
+  </si>
+  <si>
     <t>炎魔火髓</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em21</t>
+  </si>
+  <si>
     <t>‌冰蝎爪</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em22</t>
+  </si>
+  <si>
     <t>冰封王陵珍宝材料</t>
   </si>
   <si>
     <t>龙龟蛋</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em23</t>
+  </si>
+  <si>
     <t>冰兽魔核</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em24</t>
+  </si>
+  <si>
     <t>鬼面毒囊</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em25</t>
+  </si>
+  <si>
     <t>暗影祭坛珍宝材料</t>
   </si>
   <si>
     <t>巨蜥毒牙</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em26</t>
+  </si>
+  <si>
     <t>暗影徽记</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em27</t>
+  </si>
+  <si>
     <t>巨熊掌</t>
+  </si>
+  <si>
+    <t>ItemLogo/Exclusive_Metal/em28</t>
   </si>
   <si>
     <t>蛮族之地珍宝材料</t>
@@ -1319,31 +1139,55 @@
     </r>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em29</t>
+  </si>
+  <si>
     <t>亲卫令牌</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em30</t>
+  </si>
+  <si>
     <t>魔瞳</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em31</t>
+  </si>
+  <si>
     <t>虚空裂谷珍宝材料</t>
   </si>
   <si>
     <t>血镰刀</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em32</t>
+  </si>
+  <si>
     <t>神秘法杖</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em33</t>
+  </si>
+  <si>
     <t>犬牙</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em34</t>
+  </si>
+  <si>
     <t>地狱烈焰珍宝材料</t>
   </si>
   <si>
     <t>恶魔利爪</t>
   </si>
   <si>
+    <t>ItemLogo/Exclusive_Metal/em35</t>
+  </si>
+  <si>
     <t>深渊巨刃</t>
+  </si>
+  <si>
+    <t>ItemLogo/Exclusive_Metal/em36</t>
   </si>
 </sst>
 </file>
@@ -3977,7 +3821,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N119"/>
+  <dimension ref="C1:N76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4670,52 +4514,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C23" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>169</v>
-      </c>
+    <row r="23" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C23" s="10"/>
+      <c r="D23" s="13"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3">
-        <v>7</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1</v>
-      </c>
-      <c r="I23" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>6</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="3">
-        <v>7002</v>
+        <v>5101</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3">
         <v>1</v>
@@ -4727,9 +4552,8 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>7</v>
-      </c>
-      <c r="L24" s="3"/>
+        <v>6</v>
+      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -4737,95 +4561,107 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+    <row r="25" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C25" s="3">
+        <v>5102</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3">
+        <v>5</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C26" s="3">
+        <v>5201</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>173</v>
+      </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="F26" s="3">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>6</v>
+      </c>
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
-        <v>4001</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E27" s="2"/>
+        <v>5202</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="3"/>
       <c r="F27" s="3">
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="H27" s="3">
-        <v>1</v>
-      </c>
-      <c r="I27" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C28" s="3">
-        <v>4002</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3">
-        <v>5</v>
-      </c>
-      <c r="G28" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
-        <v>99999999999</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>5</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C28" s="10"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="3">
-        <v>4003</v>
+        <v>7001</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" s="3"/>
       <c r="F29" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>178</v>
@@ -4840,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -4851,14 +4687,14 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
-        <v>4004</v>
+        <v>7002</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>179</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>180</v>
@@ -4873,8 +4709,9 @@
         <v>0</v>
       </c>
       <c r="K30" s="3">
-        <v>5</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="L30" s="3"/>
       <c r="M30" s="3">
         <v>0</v>
       </c>
@@ -4882,184 +4719,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C31" s="3">
-        <v>4005</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="3">
-        <v>5</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H31" s="3">
-        <v>1</v>
-      </c>
-      <c r="I31" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>5</v>
-      </c>
-      <c r="M31" s="3">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C33" s="3">
-        <v>4007</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="3">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" s="3">
-        <v>1</v>
-      </c>
-      <c r="I33" s="3">
-        <v>9999999999</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C34" s="3">
-        <v>4008</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3">
-        <v>5</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="H34" s="3">
-        <v>1</v>
-      </c>
-      <c r="I34" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>5</v>
-      </c>
-      <c r="M34" s="3">
-        <v>0</v>
-      </c>
-      <c r="N34" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C35" s="3">
-        <v>4009</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="3">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H35" s="3">
-        <v>1</v>
-      </c>
-      <c r="I35" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C36" s="3">
-        <v>4010</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3">
-        <v>5</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="H36" s="3">
-        <v>1</v>
-      </c>
-      <c r="I36" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>5</v>
-      </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-      <c r="N36" s="3">
-        <v>0</v>
-      </c>
+    <row r="32" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
     </row>
     <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C37" s="3">
-        <v>4011</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>191</v>
+        <v>8001</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3">
         <v>5</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="H37" s="3">
         <v>1</v>
@@ -5080,19 +4765,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C38" s="3">
+        <v>8002</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3">
+        <v>5</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H38" s="3">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>6</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0</v>
+      </c>
+    </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="3">
-        <v>4013</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>193</v>
+        <v>8003</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -5104,7 +4822,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M39" s="3">
         <v>0</v>
@@ -5115,17 +4833,17 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C40" s="3">
-        <v>4015</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>195</v>
+        <v>8004</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3">
         <v>5</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -5148,17 +4866,17 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C41" s="3">
-        <v>4016</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>197</v>
+        <v>8005</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3">
         <v>5</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
@@ -5181,17 +4899,17 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
-        <v>4017</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>199</v>
+        <v>8006</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="H42" s="3">
         <v>1</v>
@@ -5203,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -5214,17 +4932,17 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
-        <v>4018</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>201</v>
+        <v>8007</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="H43" s="3">
         <v>1</v>
@@ -5247,17 +4965,17 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
-        <v>4019</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>203</v>
+        <v>8008</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -5269,28 +4987,61 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>6</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C45" s="3">
+        <v>8009</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" s="3">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>7</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
-        <v>4021</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>205</v>
+        <v>8010</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3">
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="H46" s="3">
         <v>1</v>
@@ -5302,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -5313,17 +5064,17 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
-        <v>4022</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>207</v>
+        <v>8011</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>193</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5335,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -5346,17 +5097,17 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
-        <v>4023</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>209</v>
+        <v>8012</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>194</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="H48" s="3">
         <v>1</v>
@@ -5368,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -5379,17 +5130,17 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
-        <v>4024</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>211</v>
+        <v>8013</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3">
         <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -5401,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -5412,17 +5163,17 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
-        <v>4025</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>213</v>
+        <v>8014</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>196</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3">
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5445,17 +5196,17 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
-        <v>4026</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>215</v>
+        <v>8015</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="3">
         <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
@@ -5467,7 +5218,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -5478,17 +5229,17 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
-        <v>4027</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>217</v>
+        <v>8016</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3">
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5509,196 +5260,173 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C53" s="3">
-        <v>4028</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="3">
+    <row r="54" customHeight="1" spans="3:14">
+      <c r="C54" s="3">
+        <v>8201</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="3">
+        <v>16</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
+        <v>1</v>
+      </c>
+      <c r="L54" s="3">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:14">
+      <c r="C55" s="3">
+        <v>8202</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="F55" s="3">
+        <v>16</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+      <c r="K55" s="3">
+        <v>2</v>
+      </c>
+      <c r="L55" s="3">
+        <v>0</v>
+      </c>
+      <c r="M55" s="3">
+        <v>0</v>
+      </c>
+      <c r="N55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:14">
+      <c r="C56" s="3">
+        <v>8203</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F56" s="3">
+        <v>16</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="3">
+        <v>1</v>
+      </c>
+      <c r="I56" s="3">
+        <v>1</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
+        <v>3</v>
+      </c>
+      <c r="L56" s="3">
+        <v>0</v>
+      </c>
+      <c r="M56" s="3">
+        <v>0</v>
+      </c>
+      <c r="N56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:14">
+      <c r="C57" s="3">
+        <v>8204</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="F57" s="3">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1</v>
+      </c>
+      <c r="I57" s="3">
+        <v>1</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:14">
+      <c r="C58" s="3">
+        <v>8205</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" s="3">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3">
+        <v>1</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>5</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H53" s="3">
-        <v>1</v>
-      </c>
-      <c r="I53" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3">
-        <v>7</v>
-      </c>
-      <c r="M53" s="3">
-        <v>0</v>
-      </c>
-      <c r="N53" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C54" s="3">
-        <v>4029</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3">
-        <v>5</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1</v>
-      </c>
-      <c r="I54" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>7</v>
-      </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
-      <c r="N54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C55" s="3">
-        <v>4030</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="3">
-        <v>5</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H55" s="3">
-        <v>1</v>
-      </c>
-      <c r="I55" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>7</v>
-      </c>
-      <c r="M55" s="3">
-        <v>0</v>
-      </c>
-      <c r="N55" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C56" s="3">
-        <v>4031</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="3">
-        <v>5</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H56" s="3">
-        <v>1</v>
-      </c>
-      <c r="I56" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
-        <v>7</v>
-      </c>
-      <c r="M56" s="3">
-        <v>0</v>
-      </c>
-      <c r="N56" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C57" s="3">
-        <v>4032</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="3">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1</v>
-      </c>
-      <c r="I57" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>7</v>
-      </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C58" s="3">
-        <v>4033</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="3">
-        <v>5</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H58" s="3">
-        <v>1</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>6</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5707,31 +5435,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="59" customHeight="1" spans="3:14">
       <c r="C59" s="3">
-        <v>4034</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E59" s="2"/>
+        <v>8206</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>209</v>
+      </c>
       <c r="F59" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
       </c>
       <c r="I59" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5740,25 +5470,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" s="3" customFormat="1" customHeight="1" spans="3:14">
+    <row r="60" customHeight="1" spans="3:14">
       <c r="C60" s="3">
-        <v>4035</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E60" s="2"/>
+        <v>8207</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>211</v>
+      </c>
       <c r="F60" s="3">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="H60" s="3">
         <v>1</v>
       </c>
       <c r="I60" s="3">
-        <v>9999999</v>
+        <v>1</v>
       </c>
       <c r="J60" s="3">
         <v>0</v>
@@ -5766,6 +5495,9 @@
       <c r="K60" s="3">
         <v>7</v>
       </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5773,1279 +5505,51 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C61" s="3">
-        <v>4037</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" s="3">
-        <v>5</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="H61" s="3">
-        <v>1</v>
-      </c>
-      <c r="I61" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>9</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C62" s="3">
-        <v>4038</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" s="3">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1</v>
-      </c>
-      <c r="I62" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>9</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C63" s="3">
-        <v>4039</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" s="3">
-        <v>5</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H63" s="3">
-        <v>1</v>
-      </c>
-      <c r="I63" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>8</v>
-      </c>
-      <c r="M63" s="3">
-        <v>0</v>
-      </c>
-      <c r="N63" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C64" s="3">
-        <v>4040</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" s="3">
-        <v>5</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H64" s="3">
-        <v>1</v>
-      </c>
-      <c r="I64" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3">
-        <v>6</v>
-      </c>
-      <c r="M64" s="3">
-        <v>0</v>
-      </c>
-      <c r="N64" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C65" s="3">
-        <v>4041</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" s="3">
-        <v>5</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="H65" s="3">
-        <v>1</v>
-      </c>
-      <c r="I65" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>8</v>
-      </c>
-      <c r="M65" s="3">
-        <v>0</v>
-      </c>
-      <c r="N65" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C66" s="3">
-        <v>4042</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" s="3">
-        <v>5</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1999999999</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
-      <c r="N66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C67" s="3">
-        <v>4043</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="3">
-        <v>5</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="H67" s="3">
-        <v>1</v>
-      </c>
-      <c r="I67" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0</v>
-      </c>
-      <c r="K67" s="3">
-        <v>7</v>
-      </c>
-      <c r="M67" s="3">
-        <v>0</v>
-      </c>
-      <c r="N67" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C68" s="3">
-        <v>4044</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" s="3">
-        <v>5</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="H68" s="3">
-        <v>1</v>
-      </c>
-      <c r="I68" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J68" s="3">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3">
-        <v>9</v>
-      </c>
-      <c r="M68" s="3">
-        <v>0</v>
-      </c>
-      <c r="N68" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C70" s="3">
-        <v>4101</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" s="3">
-        <v>5</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H70" s="3">
-        <v>1</v>
-      </c>
-      <c r="I70" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>5</v>
-      </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C71" s="3">
-        <v>4111</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" s="3">
-        <v>5</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="H71" s="3">
-        <v>1</v>
-      </c>
-      <c r="I71" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J71" s="3">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3">
-        <v>5</v>
-      </c>
-      <c r="M71" s="3">
-        <v>0</v>
-      </c>
-      <c r="N71" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C72" s="3">
-        <v>4112</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" s="3">
-        <v>5</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H72" s="3">
-        <v>1</v>
-      </c>
-      <c r="I72" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C73" s="3">
-        <v>4113</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" s="3">
-        <v>5</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H73" s="3">
-        <v>1</v>
-      </c>
-      <c r="I73" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>7</v>
-      </c>
-      <c r="M73" s="3">
-        <v>0</v>
-      </c>
-      <c r="N73" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C75" s="3">
-        <v>4201</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" s="3">
-        <v>5</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H75" s="3">
-        <v>1</v>
-      </c>
-      <c r="I75" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>5</v>
-      </c>
-      <c r="M75" s="3">
-        <v>4002</v>
-      </c>
-      <c r="N75" s="3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="80" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C80" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" s="3">
-        <v>5</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H80" s="3">
-        <v>1</v>
-      </c>
-      <c r="I80" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3">
-        <v>6</v>
-      </c>
-      <c r="M80" s="3">
-        <v>0</v>
-      </c>
-      <c r="N80" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C81" s="3">
-        <v>8002</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" s="3">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H81" s="3">
-        <v>1</v>
-      </c>
-      <c r="I81" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>6</v>
-      </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C82" s="3">
-        <v>8003</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" s="3">
-        <v>5</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H82" s="3">
-        <v>1</v>
-      </c>
-      <c r="I82" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J82" s="3">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3">
-        <v>6</v>
-      </c>
-      <c r="M82" s="3">
-        <v>0</v>
-      </c>
-      <c r="N82" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C83" s="3">
-        <v>8004</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="3">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1</v>
-      </c>
-      <c r="I83" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C84" s="3">
-        <v>8005</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" s="3">
-        <v>5</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H84" s="3">
-        <v>1</v>
-      </c>
-      <c r="I84" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J84" s="3">
-        <v>0</v>
-      </c>
-      <c r="K84" s="3">
-        <v>6</v>
-      </c>
-      <c r="M84" s="3">
-        <v>0</v>
-      </c>
-      <c r="N84" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C85" s="3">
-        <v>8006</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" s="3">
-        <v>5</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H85" s="3">
-        <v>1</v>
-      </c>
-      <c r="I85" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>6</v>
-      </c>
-      <c r="M85" s="3">
-        <v>0</v>
-      </c>
-      <c r="N85" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C86" s="3">
-        <v>8007</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" s="3">
-        <v>5</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H86" s="3">
-        <v>1</v>
-      </c>
-      <c r="I86" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>6</v>
-      </c>
-      <c r="M86" s="3">
-        <v>0</v>
-      </c>
-      <c r="N86" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C87" s="3">
-        <v>8008</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" s="3">
-        <v>5</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="H87" s="3">
-        <v>1</v>
-      </c>
-      <c r="I87" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3">
-        <v>6</v>
-      </c>
-      <c r="M87" s="3">
-        <v>0</v>
-      </c>
-      <c r="N87" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C88" s="3">
-        <v>8009</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" s="3">
-        <v>5</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H88" s="3">
-        <v>1</v>
-      </c>
-      <c r="I88" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3">
-        <v>7</v>
-      </c>
-      <c r="M88" s="3">
-        <v>0</v>
-      </c>
-      <c r="N88" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C89" s="3">
-        <v>8010</v>
-      </c>
-      <c r="D89" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" s="3">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H89" s="3">
-        <v>1</v>
-      </c>
-      <c r="I89" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>7</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C90" s="3">
-        <v>8011</v>
-      </c>
-      <c r="D90" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" s="3">
-        <v>5</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H90" s="3">
-        <v>1</v>
-      </c>
-      <c r="I90" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>7</v>
-      </c>
-      <c r="M90" s="3">
-        <v>0</v>
-      </c>
-      <c r="N90" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C91" s="3">
-        <v>8012</v>
-      </c>
-      <c r="D91" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" s="3">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H91" s="3">
-        <v>1</v>
-      </c>
-      <c r="I91" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>7</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C92" s="3">
-        <v>8013</v>
-      </c>
-      <c r="D92" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" s="3">
-        <v>5</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H92" s="3">
-        <v>1</v>
-      </c>
-      <c r="I92" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3">
-        <v>7</v>
-      </c>
-      <c r="M92" s="3">
-        <v>0</v>
-      </c>
-      <c r="N92" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C93" s="3">
-        <v>8014</v>
-      </c>
-      <c r="D93" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" s="3">
-        <v>5</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H93" s="3">
-        <v>1</v>
-      </c>
-      <c r="I93" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>7</v>
-      </c>
-      <c r="M93" s="3">
-        <v>0</v>
-      </c>
-      <c r="N93" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C94" s="3">
-        <v>8015</v>
-      </c>
-      <c r="D94" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" s="3">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H94" s="3">
-        <v>1</v>
-      </c>
-      <c r="I94" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>7</v>
-      </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C95" s="3">
-        <v>8016</v>
-      </c>
-      <c r="D95" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" s="3">
-        <v>5</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H95" s="3">
-        <v>1</v>
-      </c>
-      <c r="I95" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>7</v>
-      </c>
-      <c r="M95" s="3">
-        <v>0</v>
-      </c>
-      <c r="N95" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" customHeight="1" spans="3:14">
-      <c r="C97" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D97" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="F97" s="3">
-        <v>16</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H97" s="3">
-        <v>1</v>
-      </c>
-      <c r="I97" s="3">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <v>1</v>
-      </c>
-      <c r="L97" s="3">
-        <v>0</v>
-      </c>
-      <c r="M97" s="3">
-        <v>0</v>
-      </c>
-      <c r="N97" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customHeight="1" spans="3:14">
-      <c r="C98" s="3">
-        <v>8202</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F98" s="3">
-        <v>16</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H98" s="3">
-        <v>1</v>
-      </c>
-      <c r="I98" s="3">
-        <v>1</v>
-      </c>
-      <c r="J98" s="3">
-        <v>0</v>
-      </c>
-      <c r="K98" s="3">
-        <v>2</v>
-      </c>
-      <c r="L98" s="3">
-        <v>0</v>
-      </c>
-      <c r="M98" s="3">
-        <v>0</v>
-      </c>
-      <c r="N98" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" customHeight="1" spans="3:14">
-      <c r="C99" s="3">
-        <v>8203</v>
-      </c>
-      <c r="D99" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="F99" s="3">
-        <v>16</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="H99" s="3">
-        <v>1</v>
-      </c>
-      <c r="I99" s="3">
-        <v>1</v>
-      </c>
-      <c r="J99" s="3">
-        <v>0</v>
-      </c>
-      <c r="K99" s="3">
-        <v>3</v>
-      </c>
-      <c r="L99" s="3">
-        <v>0</v>
-      </c>
-      <c r="M99" s="3">
-        <v>0</v>
-      </c>
-      <c r="N99" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="3:14">
-      <c r="C100" s="3">
-        <v>8204</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F100" s="3">
-        <v>16</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="H100" s="3">
-        <v>1</v>
-      </c>
-      <c r="I100" s="3">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>4</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:14">
-      <c r="C101" s="3">
-        <v>8205</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="F101" s="3">
-        <v>16</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H101" s="3">
-        <v>1</v>
-      </c>
-      <c r="I101" s="3">
-        <v>1</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:14">
-      <c r="C102" s="3">
-        <v>8206</v>
-      </c>
-      <c r="D102" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="F102" s="3">
-        <v>16</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H102" s="3">
-        <v>1</v>
-      </c>
-      <c r="I102" s="3">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3">
-        <v>6</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:14">
-      <c r="C103" s="3">
-        <v>8207</v>
-      </c>
-      <c r="D103" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="F103" s="3">
-        <v>16</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="H103" s="3">
-        <v>1</v>
-      </c>
-      <c r="I103" s="3">
-        <v>1</v>
-      </c>
-      <c r="J103" s="3">
-        <v>0</v>
-      </c>
-      <c r="K103" s="3">
-        <v>7</v>
-      </c>
-      <c r="L103" s="3">
-        <v>0</v>
-      </c>
-      <c r="M103" s="3">
-        <v>0</v>
-      </c>
-      <c r="N103" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:14">
-      <c r="D105" s="11"/>
-    </row>
-    <row r="106" customHeight="1" spans="3:14">
-      <c r="D106" s="11"/>
-    </row>
-    <row r="107" customHeight="1" spans="3:14">
-      <c r="D107" s="11"/>
-    </row>
-    <row r="108" customHeight="1" spans="3:14">
-      <c r="D108" s="11"/>
-    </row>
-    <row r="109" customHeight="1" spans="3:14">
-      <c r="D109" s="11"/>
-    </row>
-    <row r="110" customHeight="1" spans="3:14">
-      <c r="D110" s="11"/>
-    </row>
-    <row r="111" customHeight="1" spans="3:14">
-      <c r="D111" s="11"/>
-    </row>
-    <row r="113" customHeight="1" spans="4:4">
-      <c r="D113" s="11"/>
-    </row>
-    <row r="114" customHeight="1" spans="4:4">
-      <c r="D114" s="11"/>
-    </row>
-    <row r="115" customHeight="1" spans="4:4">
-      <c r="D115" s="11"/>
-    </row>
-    <row r="116" customHeight="1" spans="4:4">
-      <c r="D116" s="11"/>
-    </row>
-    <row r="117" customHeight="1" spans="4:4">
-      <c r="D117" s="11"/>
-    </row>
-    <row r="118" customHeight="1" spans="4:4">
-      <c r="D118" s="11"/>
-    </row>
-    <row r="119" customHeight="1" spans="4:4">
-      <c r="D119" s="11"/>
+    <row r="62" customHeight="1" spans="3:14">
+      <c r="D62" s="11"/>
+    </row>
+    <row r="63" customHeight="1" spans="3:14">
+      <c r="D63" s="11"/>
+    </row>
+    <row r="64" customHeight="1" spans="3:14">
+      <c r="D64" s="11"/>
+    </row>
+    <row r="65" customHeight="1" spans="4:4">
+      <c r="D65" s="11"/>
+    </row>
+    <row r="66" customHeight="1" spans="4:4">
+      <c r="D66" s="11"/>
+    </row>
+    <row r="67" customHeight="1" spans="4:4">
+      <c r="D67" s="11"/>
+    </row>
+    <row r="68" customHeight="1" spans="4:4">
+      <c r="D68" s="11"/>
+    </row>
+    <row r="70" customHeight="1" spans="4:4">
+      <c r="D70" s="11"/>
+    </row>
+    <row r="71" customHeight="1" spans="4:4">
+      <c r="D71" s="11"/>
+    </row>
+    <row r="72" customHeight="1" spans="4:4">
+      <c r="D72" s="11"/>
+    </row>
+    <row r="73" customHeight="1" spans="4:4">
+      <c r="D73" s="11"/>
+    </row>
+    <row r="74" customHeight="1" spans="4:4">
+      <c r="D74" s="11"/>
+    </row>
+    <row r="75" customHeight="1" spans="4:4">
+      <c r="D75" s="11"/>
+    </row>
+    <row r="76" customHeight="1" spans="4:4">
+      <c r="D76" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C14:C17 C3:E5 C18:D22" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C23:D23 D25 D27 C28:D28 C14:C17 C3:E5 C18:D22" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -7197,14 +5701,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7227,14 +5731,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7257,14 +5761,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7287,14 +5791,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -7317,14 +5821,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -7347,14 +5851,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -7376,14 +5880,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -7405,14 +5909,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -7434,14 +5938,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -7463,14 +5967,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -7492,14 +5996,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -7676,14 +6180,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -7705,14 +6209,14 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -7734,14 +6238,14 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -7763,14 +6267,14 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -8041,16 +6545,16 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -8071,16 +6575,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>309</v>
+        <v>233</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -8101,16 +6605,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>311</v>
+        <v>235</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>312</v>
+        <v>236</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -8131,16 +6635,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>313</v>
+        <v>237</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>314</v>
+        <v>238</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -8161,16 +6665,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>316</v>
+        <v>240</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>317</v>
+        <v>241</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -8191,16 +6695,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>319</v>
+        <v>243</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>315</v>
+        <v>239</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -8223,16 +6727,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>320</v>
+        <v>244</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>321</v>
+        <v>245</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -8252,16 +6756,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>323</v>
+        <v>247</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -8281,16 +6785,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>325</v>
+        <v>249</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -8310,16 +6814,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>327</v>
+        <v>251</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -8339,16 +6843,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>330</v>
+        <v>254</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>331</v>
+        <v>255</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -8369,16 +6873,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>332</v>
+        <v>256</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>333</v>
+        <v>257</v>
       </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -8398,14 +6902,16 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E18" s="3"/>
+        <v>258</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>259</v>
+      </c>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>335</v>
+        <v>260</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -8425,14 +6931,16 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E19" s="3"/>
+        <v>261</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>335</v>
+        <v>260</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -8452,14 +6960,16 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="E20" s="3"/>
+        <v>263</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>264</v>
+      </c>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>335</v>
+        <v>260</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -8479,14 +6989,16 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E21" s="3"/>
+        <v>265</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -8506,14 +7018,16 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E22" s="3"/>
+        <v>268</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>269</v>
+      </c>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -8533,14 +7047,16 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E23" s="3"/>
+        <v>270</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>339</v>
+        <v>267</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -8560,13 +7076,16 @@
         <v>40000019</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>342</v>
+        <v>272</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="F24" s="2">
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -8586,13 +7105,16 @@
         <v>40000020</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>344</v>
+        <v>275</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="F25" s="2">
         <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -8612,13 +7134,16 @@
         <v>40000021</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>345</v>
+        <v>277</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>278</v>
       </c>
       <c r="F26" s="2">
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>343</v>
+        <v>274</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -8638,13 +7163,16 @@
         <v>40000022</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>346</v>
+        <v>279</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>280</v>
       </c>
       <c r="F27" s="2">
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -8664,13 +7192,16 @@
         <v>40000023</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>348</v>
+        <v>282</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="F28" s="2">
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -8690,13 +7221,16 @@
         <v>40000024</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>349</v>
+        <v>284</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>285</v>
       </c>
       <c r="F29" s="2">
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -8716,13 +7250,16 @@
         <v>40000025</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>350</v>
+        <v>286</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>287</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -8742,13 +7279,16 @@
         <v>40000026</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>352</v>
+        <v>289</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -8768,13 +7308,16 @@
         <v>40000027</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>353</v>
+        <v>291</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="F32" s="2">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -8794,13 +7337,16 @@
         <v>40000028</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>354</v>
+        <v>293</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="F33" s="2">
         <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -8820,13 +7366,16 @@
         <v>40000029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>356</v>
+        <v>296</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="F34" s="2">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -8846,13 +7395,16 @@
         <v>40000030</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>357</v>
+        <v>298</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="F35" s="2">
         <v>6</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>355</v>
+        <v>295</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -8872,13 +7424,16 @@
         <v>40000031</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>358</v>
+        <v>300</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="F36" s="2">
         <v>6</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -8898,13 +7453,16 @@
         <v>40000032</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>360</v>
+        <v>303</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="F37" s="2">
         <v>6</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -8924,13 +7482,16 @@
         <v>40000033</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>361</v>
+        <v>305</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="F38" s="2">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>359</v>
+        <v>302</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -8950,13 +7511,16 @@
         <v>40000034</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>362</v>
+        <v>307</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="F39" s="2">
         <v>6</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -8976,13 +7540,16 @@
         <v>40000035</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>364</v>
+        <v>310</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>311</v>
       </c>
       <c r="F40" s="2">
         <v>6</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -9002,13 +7569,16 @@
         <v>40000036</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>365</v>
+        <v>312</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>313</v>
       </c>
       <c r="F41" s="2">
         <v>6</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>363</v>
+        <v>309</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="技能" sheetId="1" r:id="rId1"/>
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="316">
   <si>
     <t>_Id</t>
   </si>
@@ -682,6 +682,12 @@
   </si>
   <si>
     <t>升级技能，获得5点技能经验</t>
+  </si>
+  <si>
+    <t>凤凰之羽</t>
+  </si>
+  <si>
+    <t>升级翅膀</t>
   </si>
   <si>
     <t>灵盾碎片</t>
@@ -3821,7 +3827,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N76"/>
+  <dimension ref="C1:N77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4194,57 +4200,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C13" s="3">
+        <v>5008</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>5</v>
+      </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C14" s="10">
-        <v>5011</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="12">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1</v>
-      </c>
-      <c r="I14" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>3</v>
-      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C15" s="10">
-        <v>5012</v>
+        <v>5011</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>153</v>
@@ -4278,12 +4284,12 @@
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C16" s="10">
-        <v>5013</v>
+        <v>5012</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="12">
         <v>5</v>
       </c>
@@ -4312,7 +4318,7 @@
     </row>
     <row r="17" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C17" s="10">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>157</v>
@@ -4346,16 +4352,16 @@
     </row>
     <row r="18" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C18" s="10">
-        <v>5015</v>
-      </c>
-      <c r="D18" s="13" t="s">
+        <v>5014</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>159</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="12">
         <v>5</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="3" t="s">
         <v>160</v>
       </c>
       <c r="H18" s="3">
@@ -4367,10 +4373,10 @@
       <c r="J18" s="3">
         <v>0</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="3">
         <v>3</v>
       </c>
-      <c r="L18" s="10"/>
+      <c r="L18" s="3"/>
       <c r="M18" s="3">
         <v>0</v>
       </c>
@@ -4380,7 +4386,7 @@
     </row>
     <row r="19" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C19" s="10">
-        <v>5016</v>
+        <v>5015</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>161</v>
@@ -4414,7 +4420,7 @@
     </row>
     <row r="20" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C20" s="10">
-        <v>5017</v>
+        <v>5016</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>163</v>
@@ -4436,7 +4442,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L20" s="10"/>
       <c r="M20" s="3">
@@ -4448,7 +4454,7 @@
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="10">
-        <v>5018</v>
+        <v>5017</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>165</v>
@@ -4482,7 +4488,7 @@
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="10">
-        <v>5019</v>
+        <v>5018</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>167</v>
@@ -4504,7 +4510,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" s="10"/>
       <c r="M22" s="3">
@@ -4515,135 +4521,155 @@
       </c>
     </row>
     <row r="23" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C23" s="10"/>
-      <c r="D23" s="13"/>
+      <c r="C23" s="10">
+        <v>5019</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>169</v>
+      </c>
       <c r="E23" s="3"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="10"/>
+      <c r="F23" s="12">
+        <v>5</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>5</v>
+      </c>
       <c r="L23" s="10"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C24" s="3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C24" s="10"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C25" s="3">
         <v>5101</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1</v>
-      </c>
-      <c r="I24" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>6</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C25" s="3">
-        <v>5102</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="3"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="3">
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>6</v>
+      </c>
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="3">
-        <v>5201</v>
-      </c>
-      <c r="D26" s="3" t="s">
+        <v>5102</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="3"/>
       <c r="F26" s="3">
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="H26" s="3">
-        <v>1</v>
-      </c>
-      <c r="I26" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>6</v>
-      </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="3">
-        <v>5202</v>
-      </c>
-      <c r="D27" s="13" t="s">
+        <v>5201</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E27" s="3"/>
+      <c r="E27" s="2"/>
       <c r="F27" s="3">
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>6</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" s="6" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C28" s="10"/>
-      <c r="D28" s="13"/>
+      <c r="C28" s="3">
+        <v>5202</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>177</v>
+      </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13"/>
+      <c r="F28" s="3">
+        <v>5</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -4652,47 +4678,28 @@
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
     </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C29" s="3">
-        <v>7001</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>177</v>
-      </c>
+    <row r="29" s="6" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C29" s="10"/>
+      <c r="D29" s="13"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="3">
-        <v>7</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1</v>
-      </c>
-      <c r="I29" s="3">
-        <v>9999999</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>6</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="3">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" s="3"/>
       <c r="F30" s="3">
         <v>7</v>
       </c>
@@ -4709,65 +4716,65 @@
         <v>0</v>
       </c>
       <c r="K30" s="3">
+        <v>6</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C31" s="3">
+        <v>7002</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3">
         <v>7</v>
       </c>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="37" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C37" s="3">
-        <v>8001</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3">
-        <v>5</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="H37" s="3">
-        <v>1</v>
-      </c>
-      <c r="I37" s="3">
+      <c r="H31" s="3">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
         <v>9999999</v>
       </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>6</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-      <c r="N37" s="3">
-        <v>0</v>
-      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
+        <v>7</v>
+      </c>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
     </row>
     <row r="38" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C38" s="3">
-        <v>8002</v>
+        <v>8001</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>183</v>
@@ -4777,7 +4784,7 @@
         <v>5</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -4800,17 +4807,17 @@
     </row>
     <row r="39" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C39" s="3">
-        <v>8003</v>
+        <v>8002</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3">
         <v>5</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -4833,17 +4840,17 @@
     </row>
     <row r="40" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C40" s="3">
-        <v>8004</v>
+        <v>8003</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3">
         <v>5</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -4866,17 +4873,17 @@
     </row>
     <row r="41" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C41" s="3">
-        <v>8005</v>
+        <v>8004</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3">
         <v>5</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
@@ -4899,17 +4906,17 @@
     </row>
     <row r="42" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C42" s="3">
-        <v>8006</v>
+        <v>8005</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3">
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H42" s="3">
         <v>1</v>
@@ -4932,17 +4939,17 @@
     </row>
     <row r="43" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C43" s="3">
-        <v>8007</v>
+        <v>8006</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H43" s="3">
         <v>1</v>
@@ -4965,17 +4972,17 @@
     </row>
     <row r="44" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C44" s="3">
-        <v>8008</v>
+        <v>8007</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -4998,17 +5005,17 @@
     </row>
     <row r="45" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C45" s="3">
-        <v>8009</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>190</v>
+        <v>8008</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H45" s="3">
         <v>1</v>
@@ -5020,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -5031,7 +5038,7 @@
     </row>
     <row r="46" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C46" s="3">
-        <v>8010</v>
+        <v>8009</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>192</v>
@@ -5041,7 +5048,7 @@
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H46" s="3">
         <v>1</v>
@@ -5064,17 +5071,17 @@
     </row>
     <row r="47" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C47" s="3">
-        <v>8011</v>
+        <v>8010</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5097,17 +5104,17 @@
     </row>
     <row r="48" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C48" s="3">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H48" s="3">
         <v>1</v>
@@ -5130,17 +5137,17 @@
     </row>
     <row r="49" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C49" s="3">
-        <v>8013</v>
+        <v>8012</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3">
         <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -5163,17 +5170,17 @@
     </row>
     <row r="50" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C50" s="3">
-        <v>8014</v>
+        <v>8013</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3">
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5196,17 +5203,17 @@
     </row>
     <row r="51" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C51" s="3">
-        <v>8015</v>
+        <v>8014</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="3">
         <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
@@ -5229,17 +5236,17 @@
     </row>
     <row r="52" s="3" customFormat="1" customHeight="1" spans="3:14">
       <c r="C52" s="3">
-        <v>8016</v>
+        <v>8015</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3">
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5260,44 +5267,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customHeight="1" spans="3:14">
-      <c r="C54" s="3">
-        <v>8201</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="3">
-        <v>16</v>
-      </c>
-      <c r="G54" s="3" t="s">
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C53" s="3">
+        <v>8016</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="H54" s="3">
-        <v>1</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1</v>
-      </c>
-      <c r="L54" s="3">
-        <v>0</v>
-      </c>
-      <c r="M54" s="3">
-        <v>0</v>
-      </c>
-      <c r="N54" s="3">
+      <c r="E53" s="2"/>
+      <c r="F53" s="3">
+        <v>5</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
+        <v>9999999</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
+        <v>7</v>
+      </c>
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:14">
       <c r="C55" s="3">
-        <v>8202</v>
+        <v>8201</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>201</v>
@@ -5318,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="3">
         <v>0</v>
@@ -5332,7 +5337,7 @@
     </row>
     <row r="56" customHeight="1" spans="3:14">
       <c r="C56" s="3">
-        <v>8203</v>
+        <v>8202</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>203</v>
@@ -5353,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -5367,7 +5372,7 @@
     </row>
     <row r="57" customHeight="1" spans="3:14">
       <c r="C57" s="3">
-        <v>8204</v>
+        <v>8203</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>205</v>
@@ -5388,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5402,7 +5407,7 @@
     </row>
     <row r="58" customHeight="1" spans="3:14">
       <c r="C58" s="3">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>207</v>
@@ -5423,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -5437,7 +5442,7 @@
     </row>
     <row r="59" customHeight="1" spans="3:14">
       <c r="C59" s="3">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>209</v>
@@ -5458,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     </row>
     <row r="60" customHeight="1" spans="3:14">
       <c r="C60" s="3">
-        <v>8207</v>
+        <v>8206</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>211</v>
@@ -5493,20 +5498,52 @@
         <v>0</v>
       </c>
       <c r="K60" s="3">
+        <v>6</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:14">
+      <c r="C61" s="3">
+        <v>8207</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="F61" s="3">
+        <v>16</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H61" s="3">
+        <v>1</v>
+      </c>
+      <c r="I61" s="3">
+        <v>1</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>7</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
-      <c r="N60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:14">
-      <c r="D62" s="11"/>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customHeight="1" spans="3:14">
       <c r="D63" s="11"/>
@@ -5526,8 +5563,8 @@
     <row r="68" customHeight="1" spans="4:4">
       <c r="D68" s="11"/>
     </row>
-    <row r="70" customHeight="1" spans="4:4">
-      <c r="D70" s="11"/>
+    <row r="69" customHeight="1" spans="4:4">
+      <c r="D69" s="11"/>
     </row>
     <row r="71" customHeight="1" spans="4:4">
       <c r="D71" s="11"/>
@@ -5547,9 +5584,12 @@
     <row r="76" customHeight="1" spans="4:4">
       <c r="D76" s="11"/>
     </row>
+    <row r="77" customHeight="1" spans="4:4">
+      <c r="D77" s="11"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C13:D13 C23:D23 D25 D27 C28:D28 C14:C17 C3:E5 C18:D22" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C14:D14 D26 D28 C29:D29 C15:C18 C3:E5 C19:D24" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:N5" errorStyle="warning">
@@ -5701,14 +5741,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -5731,14 +5771,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -5761,14 +5801,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -5791,14 +5831,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -5821,14 +5861,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -5851,14 +5891,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -5880,14 +5920,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -5909,14 +5949,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -5938,14 +5978,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -5967,14 +6007,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -5996,14 +6036,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -6180,14 +6220,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -6209,14 +6249,14 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -6238,14 +6278,14 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -6267,14 +6307,14 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -6545,16 +6585,16 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -6575,16 +6615,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="F7" s="2">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="F7" s="2">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -6605,16 +6645,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -6635,16 +6675,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -6665,16 +6705,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E10" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F10" s="2">
-        <v>6</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -6695,16 +6735,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -6727,16 +6767,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -6756,16 +6796,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F13" s="2">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="F13" s="2">
-        <v>6</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -6785,16 +6825,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -6814,16 +6854,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -6843,16 +6883,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F16" s="2">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="F16" s="2">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -6873,16 +6913,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -6902,16 +6942,16 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -6931,16 +6971,16 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E19" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F19" s="2">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="F19" s="2">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -6960,16 +7000,16 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -6989,16 +7029,16 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -7018,16 +7058,16 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F22" s="2">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="F22" s="2">
-        <v>6</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -7047,16 +7087,16 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -7076,16 +7116,16 @@
         <v>40000019</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F24" s="2">
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -7105,16 +7145,16 @@
         <v>40000020</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="F25" s="2">
-        <v>6</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -7134,16 +7174,16 @@
         <v>40000021</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F26" s="2">
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -7163,16 +7203,16 @@
         <v>40000022</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2">
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -7192,16 +7232,16 @@
         <v>40000023</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="F28" s="2">
-        <v>6</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -7221,16 +7261,16 @@
         <v>40000024</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F29" s="2">
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -7250,16 +7290,16 @@
         <v>40000025</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -7279,16 +7319,16 @@
         <v>40000026</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F31" s="2">
+        <v>6</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="F31" s="2">
-        <v>6</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -7308,16 +7348,16 @@
         <v>40000027</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F32" s="2">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -7337,16 +7377,16 @@
         <v>40000028</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F33" s="2">
         <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -7366,16 +7406,16 @@
         <v>40000029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F34" s="2">
+        <v>6</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="F34" s="2">
-        <v>6</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -7395,16 +7435,16 @@
         <v>40000030</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F35" s="2">
         <v>6</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -7424,16 +7464,16 @@
         <v>40000031</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F36" s="2">
         <v>6</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -7453,16 +7493,16 @@
         <v>40000032</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E37" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F37" s="2">
+        <v>6</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="F37" s="2">
-        <v>6</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -7482,16 +7522,16 @@
         <v>40000033</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F38" s="2">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -7511,16 +7551,16 @@
         <v>40000034</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F39" s="2">
         <v>6</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -7540,16 +7580,16 @@
         <v>40000035</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E40" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="F40" s="2">
+        <v>6</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>311</v>
-      </c>
-      <c r="F40" s="2">
-        <v>6</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>309</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -7569,16 +7609,16 @@
         <v>40000036</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F41" s="2">
         <v>6</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>

--- a/Excel/ItemConfig.xlsx
+++ b/Excel/ItemConfig.xlsx
@@ -229,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="328">
   <si>
     <t>_Id</t>
   </si>
@@ -684,196 +684,274 @@
     <t>升级技能，获得5点技能经验</t>
   </si>
   <si>
+    <t>灵盾碎片</t>
+  </si>
+  <si>
+    <t>灵盾进阶材料</t>
+  </si>
+  <si>
+    <t>灵符碎片</t>
+  </si>
+  <si>
+    <t>灵符进阶材料</t>
+  </si>
+  <si>
+    <t>灵玉碎片</t>
+  </si>
+  <si>
+    <t>灵玉进阶材料</t>
+  </si>
+  <si>
+    <t>灵珠碎片</t>
+  </si>
+  <si>
+    <t>灵珠进阶材料</t>
+  </si>
+  <si>
+    <t>1阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到1阶的材料</t>
+  </si>
+  <si>
+    <t>2阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到2阶的材料</t>
+  </si>
+  <si>
+    <t>3阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到3阶的材料</t>
+  </si>
+  <si>
+    <t>4阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到4阶的材料</t>
+  </si>
+  <si>
+    <t>5阶神兵符</t>
+  </si>
+  <si>
+    <t>神兵进阶到5阶的材料</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>分解红装获取，红装锻造材料</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>分解金装获取，红装锻造材料</t>
+  </si>
+  <si>
+    <t>红色魂晶</t>
+  </si>
+  <si>
+    <t>红色宠物培养材料</t>
+  </si>
+  <si>
+    <t>金色魂晶</t>
+  </si>
+  <si>
+    <t>金色宠物培养材料</t>
+  </si>
+  <si>
+    <t>等级丹</t>
+  </si>
+  <si>
+    <t>人物等级+1</t>
+  </si>
+  <si>
+    <t>天赋秘籍</t>
+  </si>
+  <si>
+    <t>天赋经验+500</t>
+  </si>
+  <si>
+    <t>十年魂环</t>
+  </si>
+  <si>
+    <t>升级对应魂环</t>
+  </si>
+  <si>
+    <t>百年魂环</t>
+  </si>
+  <si>
+    <t>千年魂环</t>
+  </si>
+  <si>
+    <t>万年魂环</t>
+  </si>
+  <si>
+    <t>十万魂环</t>
+  </si>
+  <si>
+    <t>百万魂环</t>
+  </si>
+  <si>
+    <t>千万魂环</t>
+  </si>
+  <si>
+    <t>亿年魂环</t>
+  </si>
+  <si>
+    <t>八蛛魂骨</t>
+  </si>
+  <si>
+    <t>升级对应魂骨</t>
+  </si>
+  <si>
+    <t>智慧头骨</t>
+  </si>
+  <si>
+    <t>蓝银皇骨</t>
+  </si>
+  <si>
+    <t>柔骨兔骨</t>
+  </si>
+  <si>
+    <t>邪魔腿骨</t>
+  </si>
+  <si>
+    <t>泰坦巨猿骨</t>
+  </si>
+  <si>
+    <t>天青牛蟒骨</t>
+  </si>
+  <si>
+    <t>魔鲸王骨</t>
+  </si>
+  <si>
+    <t>白色宠物</t>
+  </si>
+  <si>
+    <t>开启一个白色宠物</t>
+  </si>
+  <si>
+    <t>绿色宠物</t>
+  </si>
+  <si>
+    <t>开启一个绿色宠物</t>
+  </si>
+  <si>
+    <t>蓝色宠物</t>
+  </si>
+  <si>
+    <t>开启一个蓝色宠物</t>
+  </si>
+  <si>
+    <t>紫色宠物</t>
+  </si>
+  <si>
+    <t>开启一个紫色宠物</t>
+  </si>
+  <si>
+    <t>橙色宠物</t>
+  </si>
+  <si>
+    <t>开启一个橙色宠物</t>
+  </si>
+  <si>
+    <t>红色宠物</t>
+  </si>
+  <si>
+    <t>开启一个红色宠物</t>
+  </si>
+  <si>
+    <t>金色宠物</t>
+  </si>
+  <si>
+    <t>开启一个金色宠物</t>
+  </si>
+  <si>
     <t>凤凰之羽</t>
   </si>
   <si>
-    <t>升级翅膀</t>
-  </si>
-  <si>
-    <t>灵盾碎片</t>
-  </si>
-  <si>
-    <t>灵盾进阶材料</t>
-  </si>
-  <si>
-    <t>灵符碎片</t>
-  </si>
-  <si>
-    <t>灵符进阶材料</t>
-  </si>
-  <si>
-    <t>灵玉碎片</t>
-  </si>
-  <si>
-    <t>灵玉进阶材料</t>
-  </si>
-  <si>
-    <t>灵珠碎片</t>
-  </si>
-  <si>
-    <t>灵珠进阶材料</t>
-  </si>
-  <si>
-    <t>1阶神兵符</t>
-  </si>
-  <si>
-    <t>神兵进阶到1阶的材料</t>
-  </si>
-  <si>
-    <t>2阶神兵符</t>
-  </si>
-  <si>
-    <t>神兵进阶到2阶的材料</t>
-  </si>
-  <si>
-    <t>3阶神兵符</t>
-  </si>
-  <si>
-    <t>神兵进阶到3阶的材料</t>
-  </si>
-  <si>
-    <t>4阶神兵符</t>
-  </si>
-  <si>
-    <t>神兵进阶到4阶的材料</t>
-  </si>
-  <si>
-    <t>5阶神兵符</t>
-  </si>
-  <si>
-    <t>神兵进阶到5阶的材料</t>
-  </si>
-  <si>
-    <t>红装精华</t>
-  </si>
-  <si>
-    <t>分解红装获取，红装锻造材料</t>
-  </si>
-  <si>
-    <t>金装精华</t>
-  </si>
-  <si>
-    <t>分解金装获取，红装锻造材料</t>
-  </si>
-  <si>
-    <t>红色魂晶</t>
-  </si>
-  <si>
-    <t>红色宠物培养材料</t>
-  </si>
-  <si>
-    <t>金色魂晶</t>
-  </si>
-  <si>
-    <t>金色宠物培养材料</t>
-  </si>
-  <si>
-    <t>等级丹</t>
-  </si>
-  <si>
-    <t>人物等级+1</t>
-  </si>
-  <si>
-    <t>天赋秘籍</t>
-  </si>
-  <si>
-    <t>天赋经验+500</t>
-  </si>
-  <si>
-    <t>十年魂环</t>
-  </si>
-  <si>
-    <t>升级对应魂环</t>
-  </si>
-  <si>
-    <t>百年魂环</t>
-  </si>
-  <si>
-    <t>千年魂环</t>
-  </si>
-  <si>
-    <t>万年魂环</t>
-  </si>
-  <si>
-    <t>十万魂环</t>
-  </si>
-  <si>
-    <t>百万魂环</t>
-  </si>
-  <si>
-    <t>千万魂环</t>
-  </si>
-  <si>
-    <t>亿年魂环</t>
-  </si>
-  <si>
-    <t>八蛛魂骨</t>
-  </si>
-  <si>
-    <t>升级对应魂骨</t>
-  </si>
-  <si>
-    <t>智慧头骨</t>
-  </si>
-  <si>
-    <t>蓝银皇骨</t>
-  </si>
-  <si>
-    <t>柔骨兔骨</t>
-  </si>
-  <si>
-    <t>邪魔腿骨</t>
-  </si>
-  <si>
-    <t>泰坦巨猿骨</t>
-  </si>
-  <si>
-    <t>天青牛蟒骨</t>
-  </si>
-  <si>
-    <t>魔鲸王骨</t>
-  </si>
-  <si>
-    <t>白色宠物</t>
-  </si>
-  <si>
-    <t>开启一个白色宠物</t>
-  </si>
-  <si>
-    <t>绿色宠物</t>
-  </si>
-  <si>
-    <t>开启一个绿色宠物</t>
-  </si>
-  <si>
-    <t>蓝色宠物</t>
-  </si>
-  <si>
-    <t>开启一个蓝色宠物</t>
-  </si>
-  <si>
-    <t>紫色宠物</t>
-  </si>
-  <si>
-    <t>开启一个紫色宠物</t>
-  </si>
-  <si>
-    <t>橙色宠物</t>
-  </si>
-  <si>
-    <t>开启一个橙色宠物</t>
-  </si>
-  <si>
-    <t>红色宠物</t>
-  </si>
-  <si>
-    <t>开启一个红色宠物</t>
-  </si>
-  <si>
-    <t>金色宠物</t>
-  </si>
-  <si>
-    <t>开启一个金色宠物</t>
+    <t>升级翅膀核心</t>
+  </si>
+  <si>
+    <t>飞羽碎片</t>
+  </si>
+  <si>
+    <t>升级翅膀部件飞羽</t>
+  </si>
+  <si>
+    <t>肩翼碎片</t>
+  </si>
+  <si>
+    <t>升级翅膀部件肩翼</t>
+  </si>
+  <si>
+    <t>纤羽碎片</t>
+  </si>
+  <si>
+    <t>升级翅膀部件纤羽</t>
+  </si>
+  <si>
+    <r>
+      <t>尾翼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>碎片</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>升级翅膀部件尾翼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+  </si>
+  <si>
+    <t>翎羽碎片</t>
+  </si>
+  <si>
+    <t>升级翅膀部件翎羽</t>
+  </si>
+  <si>
+    <r>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>甲翼碎片</t>
+    </r>
+  </si>
+  <si>
+    <t>升级翅膀部件甲翼</t>
   </si>
   <si>
     <t>仙鉴青龙</t>
@@ -1206,7 +1284,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1262,6 +1340,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF05073B"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1408,6 +1492,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -1745,16 +1835,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1763,119 +1850,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1902,6 +1992,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2623,7 +2714,7 @@
       <c r="B13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>49</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -2667,7 +2758,7 @@
       <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="15" t="s">
         <v>52</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -2711,7 +2802,7 @@
       <c r="B15" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -2755,7 +2846,7 @@
       <c r="B16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>58</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -2799,7 +2890,7 @@
       <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>61</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -3109,7 +3200,7 @@
       <c r="B26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -3153,7 +3244,7 @@
       <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="15" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -3197,7 +3288,7 @@
       <c r="B28" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>92</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -3241,7 +3332,7 @@
       <c r="B29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>95</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -3285,7 +3376,7 @@
       <c r="B30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>98</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -3595,7 +3686,7 @@
       <c r="B39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="15" t="s">
         <v>123</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -3639,7 +3730,7 @@
       <c r="B40" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="15" t="s">
         <v>126</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -3683,7 +3774,7 @@
       <c r="B41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="15" t="s">
         <v>129</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -3727,7 +3818,7 @@
       <c r="B42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="15" t="s">
         <v>132</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -3771,7 +3862,7 @@
       <c r="B43" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="15" t="s">
         <v>135</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -3827,7 +3918,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:N77"/>
+  <dimension ref="C1:N78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="3"/>
@@ -4201,38 +4292,7 @@
       </c>
     </row>
     <row r="13" s="3" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C13" s="3">
-        <v>5008</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="3">
-        <v>5</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
-        <v>99999999</v>
-      </c>
-      <c r="J13" s="3">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3">
-        <v>5</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="3:14">
       <c r="C14" s="9"/>
@@ -4253,14 +4313,14 @@
         <v>5011</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="12">
         <v>5</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H15" s="3">
         <v>1</v>
@@ -4287,14 +4347,14 @@
         <v>5012</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="12">
         <v>5</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H16" s="3">
         <v>1</v>
@@ -4321,14 +4381,14 @@
         <v>5013</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="12">
         <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H17" s="3">
         <v>1</v>
@@ -4355,14 +4415,14 @@
         <v>5014</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="12">
         <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H18" s="3">
         <v>1</v>
@@ -4389,14 +4449,14 @@
         <v>5015</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="12">
         <v>5</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -4423,14 +4483,14 @@
         <v>5016</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="12">
         <v>5</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H20" s="3">
         <v>1</v>
@@ -4457,14 +4517,14 @@
         <v>5017</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="12">
         <v>5</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H21" s="3">
         <v>1</v>
@@ -4491,14 +4551,14 @@
         <v>5018</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="12">
         <v>5</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H22" s="3">
         <v>1</v>
@@ -4525,14 +4585,14 @@
         <v>5019</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="12">
         <v>5</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H23" s="3">
         <v>1</v>
@@ -4573,14 +4633,14 @@
         <v>5101</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3">
         <v>5</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3">
         <v>1</v>
@@ -4606,14 +4666,14 @@
         <v>5102</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3">
         <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -4628,14 +4688,14 @@
         <v>5201</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3">
         <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H27" s="3">
         <v>1</v>
@@ -4661,14 +4721,14 @@
         <v>5202</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3">
         <v>5</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -4697,14 +4757,14 @@
         <v>7001</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3">
         <v>7</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H30" s="3">
         <v>1</v>
@@ -4730,14 +4790,14 @@
         <v>7002</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="3">
         <v>7</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3">
         <v>1</v>
@@ -4777,14 +4837,14 @@
         <v>8001</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="3">
         <v>5</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H38" s="3">
         <v>1</v>
@@ -4810,14 +4870,14 @@
         <v>8002</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3">
         <v>5</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H39" s="3">
         <v>1</v>
@@ -4843,14 +4903,14 @@
         <v>8003</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3">
         <v>5</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3">
         <v>1</v>
@@ -4876,14 +4936,14 @@
         <v>8004</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3">
         <v>5</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H41" s="3">
         <v>1</v>
@@ -4909,14 +4969,14 @@
         <v>8005</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3">
         <v>5</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H42" s="3">
         <v>1</v>
@@ -4942,14 +5002,14 @@
         <v>8006</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3">
         <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H43" s="3">
         <v>1</v>
@@ -4975,14 +5035,14 @@
         <v>8007</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3">
         <v>5</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H44" s="3">
         <v>1</v>
@@ -5008,14 +5068,14 @@
         <v>8008</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H45" s="3">
         <v>1</v>
@@ -5041,14 +5101,14 @@
         <v>8009</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3">
         <v>5</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H46" s="3">
         <v>1</v>
@@ -5074,14 +5134,14 @@
         <v>8010</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3">
         <v>5</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H47" s="3">
         <v>1</v>
@@ -5107,14 +5167,14 @@
         <v>8011</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3">
         <v>5</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H48" s="3">
         <v>1</v>
@@ -5140,14 +5200,14 @@
         <v>8012</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3">
         <v>5</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H49" s="3">
         <v>1</v>
@@ -5173,14 +5233,14 @@
         <v>8013</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3">
         <v>5</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H50" s="3">
         <v>1</v>
@@ -5206,14 +5266,14 @@
         <v>8014</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" s="3">
         <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H51" s="3">
         <v>1</v>
@@ -5239,14 +5299,14 @@
         <v>8015</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="3">
         <v>5</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H52" s="3">
         <v>1</v>
@@ -5272,14 +5332,14 @@
         <v>8016</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="3">
         <v>5</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H53" s="3">
         <v>1</v>
@@ -5305,13 +5365,13 @@
         <v>8201</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F55" s="3">
         <v>16</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H55" s="3">
         <v>1</v>
@@ -5340,13 +5400,13 @@
         <v>8202</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F56" s="3">
         <v>16</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H56" s="3">
         <v>1</v>
@@ -5375,13 +5435,13 @@
         <v>8203</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F57" s="3">
         <v>16</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H57" s="3">
         <v>1</v>
@@ -5410,13 +5470,13 @@
         <v>8204</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F58" s="3">
         <v>16</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H58" s="3">
         <v>1</v>
@@ -5445,13 +5505,13 @@
         <v>8205</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F59" s="3">
         <v>16</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H59" s="3">
         <v>1</v>
@@ -5480,13 +5540,13 @@
         <v>8206</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F60" s="3">
         <v>16</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H60" s="3">
         <v>1</v>
@@ -5515,13 +5575,13 @@
         <v>8207</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F61" s="3">
         <v>16</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H61" s="3">
         <v>1</v>
@@ -5546,46 +5606,253 @@
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:14">
-      <c r="D63" s="11"/>
+      <c r="C63" s="3">
+        <v>8301</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F63" s="3">
+        <v>5</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H63" s="3">
+        <v>1</v>
+      </c>
+      <c r="I63" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+      <c r="K63" s="3">
+        <v>6</v>
+      </c>
+      <c r="L63" s="3"/>
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" customHeight="1" spans="3:14">
-      <c r="D64" s="11"/>
-    </row>
-    <row r="65" customHeight="1" spans="4:4">
-      <c r="D65" s="11"/>
-    </row>
-    <row r="66" customHeight="1" spans="4:4">
-      <c r="D66" s="11"/>
-    </row>
-    <row r="67" customHeight="1" spans="4:4">
-      <c r="D67" s="11"/>
-    </row>
-    <row r="68" customHeight="1" spans="4:4">
-      <c r="D68" s="11"/>
-    </row>
-    <row r="69" customHeight="1" spans="4:4">
-      <c r="D69" s="11"/>
-    </row>
-    <row r="71" customHeight="1" spans="4:4">
-      <c r="D71" s="11"/>
-    </row>
-    <row r="72" customHeight="1" spans="4:4">
+      <c r="C64" s="3">
+        <v>8302</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F64" s="3">
+        <v>5</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H64" s="3">
+        <v>1</v>
+      </c>
+      <c r="I64" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+      <c r="K64" s="3">
+        <v>6</v>
+      </c>
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:14">
+      <c r="C65" s="3">
+        <v>8303</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="F65" s="3">
+        <v>5</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="3">
+        <v>1</v>
+      </c>
+      <c r="I65" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
+        <v>6</v>
+      </c>
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:14">
+      <c r="C66" s="3">
+        <v>8304</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="F66" s="3">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H66" s="3">
+        <v>1</v>
+      </c>
+      <c r="I66" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
+        <v>6</v>
+      </c>
+      <c r="M66" s="3">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:14">
+      <c r="C67" s="3">
+        <v>8305</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="F67" s="3">
+        <v>5</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H67" s="3">
+        <v>1</v>
+      </c>
+      <c r="I67" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0</v>
+      </c>
+      <c r="K67" s="3">
+        <v>6</v>
+      </c>
+      <c r="M67" s="3">
+        <v>0</v>
+      </c>
+      <c r="N67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:14">
+      <c r="C68" s="3">
+        <v>8306</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="F68" s="3">
+        <v>5</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
+      </c>
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:14">
+      <c r="C69" s="3">
+        <v>8307</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F69" s="3">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H69" s="3">
+        <v>1</v>
+      </c>
+      <c r="I69" s="3">
+        <v>99999999</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
+        <v>6</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:14">
+      <c r="D70" s="11"/>
+    </row>
+    <row r="72" customHeight="1" spans="3:14">
       <c r="D72" s="11"/>
     </row>
-    <row r="73" customHeight="1" spans="4:4">
+    <row r="73" customHeight="1" spans="3:14">
       <c r="D73" s="11"/>
     </row>
-    <row r="74" customHeight="1" spans="4:4">
+    <row r="74" customHeight="1" spans="3:14">
       <c r="D74" s="11"/>
     </row>
-    <row r="75" customHeight="1" spans="4:4">
+    <row r="75" customHeight="1" spans="3:14">
       <c r="D75" s="11"/>
     </row>
-    <row r="76" customHeight="1" spans="4:4">
+    <row r="76" customHeight="1" spans="3:14">
       <c r="D76" s="11"/>
     </row>
-    <row r="77" customHeight="1" spans="4:4">
+    <row r="77" customHeight="1" spans="3:14">
       <c r="D77" s="11"/>
+    </row>
+    <row r="78" customHeight="1" spans="3:14">
+      <c r="D78" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -5741,14 +6008,14 @@
         <v>9001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -5771,14 +6038,14 @@
         <v>9002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -5801,14 +6068,14 @@
         <v>9003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -5831,14 +6098,14 @@
         <v>9004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -5861,14 +6128,14 @@
         <v>9005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -5891,14 +6158,14 @@
         <v>9006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -5920,14 +6187,14 @@
         <v>9007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -5949,14 +6216,14 @@
         <v>9008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -5978,14 +6245,14 @@
         <v>9009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -6007,14 +6274,14 @@
         <v>9010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -6036,14 +6303,14 @@
         <v>9011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -6220,14 +6487,14 @@
         <v>10001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -6249,14 +6516,14 @@
         <v>10002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -6278,14 +6545,14 @@
         <v>10003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="2">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -6307,14 +6574,14 @@
         <v>10004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -6585,16 +6852,16 @@
         <v>40000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="F6" s="2">
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H6" s="2">
         <v>1</v>
@@ -6615,16 +6882,16 @@
         <v>40000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H7" s="2">
         <v>1</v>
@@ -6645,16 +6912,16 @@
         <v>40000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F8" s="2">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="H8" s="2">
         <v>1</v>
@@ -6675,16 +6942,16 @@
         <v>40000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -6705,16 +6972,16 @@
         <v>40000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H10" s="2">
         <v>1</v>
@@ -6735,16 +7002,16 @@
         <v>40000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="F11" s="2">
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -6767,16 +7034,16 @@
         <v>40000007</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F12" s="2">
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H12" s="2">
         <v>1</v>
@@ -6796,16 +7063,16 @@
         <v>40000008</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="F13" s="2">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H13" s="2">
         <v>1</v>
@@ -6825,16 +7092,16 @@
         <v>40000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F14" s="2">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="H14" s="2">
         <v>1</v>
@@ -6854,16 +7121,16 @@
         <v>40000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="F15" s="2">
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H15" s="2">
         <v>1</v>
@@ -6883,16 +7150,16 @@
         <v>40000011</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H16" s="2">
         <v>1</v>
@@ -6913,16 +7180,16 @@
         <v>40000012</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F17" s="2">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="H17" s="2">
         <v>1</v>
@@ -6942,16 +7209,16 @@
         <v>40000013</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="F18" s="2">
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="H18" s="2">
         <v>1</v>
@@ -6971,16 +7238,16 @@
         <v>40000014</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="F19" s="2">
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="H19" s="2">
         <v>1</v>
@@ -7000,16 +7267,16 @@
         <v>40000015</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="H20" s="2">
         <v>1</v>
@@ -7029,16 +7296,16 @@
         <v>40000016</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F21" s="2">
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="H21" s="2">
         <v>1</v>
@@ -7058,16 +7325,16 @@
         <v>40000017</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="F22" s="2">
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="H22" s="2">
         <v>1</v>
@@ -7087,16 +7354,16 @@
         <v>40000018</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="F23" s="2">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="H23" s="2">
         <v>1</v>
@@ -7116,16 +7383,16 @@
         <v>40000019</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="F24" s="2">
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="H24" s="2">
         <v>1</v>
@@ -7145,16 +7412,16 @@
         <v>40000020</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="F25" s="2">
         <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="H25" s="2">
         <v>1</v>
@@ -7174,16 +7441,16 @@
         <v>40000021</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="F26" s="2">
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="H26" s="2">
         <v>1</v>
@@ -7203,16 +7470,16 @@
         <v>40000022</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="F27" s="2">
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -7232,16 +7499,16 @@
         <v>40000023</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="F28" s="2">
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H28" s="2">
         <v>1</v>
@@ -7261,16 +7528,16 @@
         <v>40000024</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="F29" s="2">
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H29" s="2">
         <v>1</v>
@@ -7290,16 +7557,16 @@
         <v>40000025</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="F30" s="2">
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="H30" s="2">
         <v>1</v>
@@ -7319,16 +7586,16 @@
         <v>40000026</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="H31" s="2">
         <v>1</v>
@@ -7348,16 +7615,16 @@
         <v>40000027</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F32" s="2">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="H32" s="2">
         <v>1</v>
@@ -7377,16 +7644,16 @@
         <v>40000028</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="F33" s="2">
         <v>6</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="H33" s="2">
         <v>1</v>
@@ -7406,16 +7673,16 @@
         <v>40000029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F34" s="2">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -7435,16 +7702,16 @@
         <v>40000030</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="F35" s="2">
         <v>6</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="H35" s="2">
         <v>1</v>
@@ -7464,16 +7731,16 @@
         <v>40000031</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F36" s="2">
         <v>6</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H36" s="2">
         <v>1</v>
@@ -7493,16 +7760,16 @@
         <v>40000032</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="F37" s="2">
         <v>6</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H37" s="2">
         <v>1</v>
@@ -7522,16 +7789,16 @@
         <v>40000033</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="F38" s="2">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H38" s="2">
         <v>1</v>
@@ -7551,16 +7818,16 @@
         <v>40000034</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="F39" s="2">
         <v>6</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H39" s="2">
         <v>1</v>
@@ -7580,16 +7847,16 @@
         <v>40000035</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="F40" s="2">
         <v>6</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H40" s="2">
         <v>1</v>
@@ -7609,16 +7876,16 @@
         <v>40000036</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="F41" s="2">
         <v>6</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H41" s="2">
         <v>1</v>
